--- a/output/roomself_excel/6343.xlsx
+++ b/output/roomself_excel/6343.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37800</v>
+        <v>206986</v>
       </c>
       <c r="D2" t="n">
-        <v>1704</v>
+        <v>3652</v>
       </c>
       <c r="E2" t="n">
-        <v>316</v>
+        <v>490</v>
       </c>
       <c r="F2" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>534067</v>
+        <v>98595</v>
       </c>
       <c r="D4" t="n">
-        <v>8940</v>
+        <v>2512</v>
       </c>
       <c r="E4" t="n">
-        <v>861</v>
+        <v>313</v>
       </c>
       <c r="F4" t="n">
-        <v>819</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>98595</v>
+        <v>118833</v>
       </c>
       <c r="D5" t="n">
-        <v>2512</v>
+        <v>2824</v>
       </c>
       <c r="E5" t="n">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="F5" t="n">
         <v>16</v>
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>118833</v>
+        <v>106368</v>
       </c>
       <c r="D6" t="n">
-        <v>2824</v>
+        <v>2644</v>
       </c>
       <c r="E6" t="n">
         <v>277</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23814</v>
+        <v>44880</v>
       </c>
       <c r="D7" t="n">
-        <v>1260</v>
+        <v>1724</v>
       </c>
       <c r="E7" t="n">
-        <v>205</v>
+        <v>255</v>
       </c>
       <c r="F7" t="n">
-        <v>142</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -602,13 +602,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44880</v>
+        <v>21505</v>
       </c>
       <c r="D8" t="n">
-        <v>1724</v>
+        <v>1208</v>
       </c>
       <c r="E8" t="n">
-        <v>255</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>33950</v>
+        <v>132401</v>
       </c>
       <c r="D9" t="n">
-        <v>1476</v>
+        <v>3308</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>106368</v>
+        <v>23814</v>
       </c>
       <c r="D10" t="n">
-        <v>2644</v>
+        <v>1260</v>
       </c>
       <c r="E10" t="n">
-        <v>277</v>
+        <v>205</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80038</v>
+        <v>37800</v>
       </c>
       <c r="D11" t="n">
-        <v>2468</v>
+        <v>1704</v>
       </c>
       <c r="E11" t="n">
-        <v>383</v>
+        <v>316</v>
       </c>
       <c r="F11" t="n">
-        <v>221</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21505</v>
+        <v>33950</v>
       </c>
       <c r="D12" t="n">
-        <v>1208</v>
+        <v>1476</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F12" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>194680</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3584</v>
+      </c>
+      <c r="E13" t="n">
+        <v>490</v>
+      </c>
+      <c r="F13" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>80038</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E14" t="n">
+        <v>383</v>
+      </c>
+      <c r="F14" t="n">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/6343.xlsx
+++ b/output/roomself_excel/6343.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>3652</v>
       </c>
-      <c r="E2" t="n">
-        <v>490</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>474</v>
+      </c>
+      <c r="G2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>2880</v>
       </c>
-      <c r="E3" t="n">
-        <v>525</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>180</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +563,20 @@
       <c r="D4" t="n">
         <v>2512</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>313</v>
       </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>2824</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>277</v>
       </c>
-      <c r="F5" t="n">
-        <v>16</v>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>429</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -563,10 +631,26 @@
       <c r="D6" t="n">
         <v>2644</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>384</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>277</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>16</v>
       </c>
     </row>
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>1724</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>255</v>
       </c>
-      <c r="F7" t="n">
-        <v>16</v>
-      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1208</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>115</v>
       </c>
-      <c r="F8" t="n">
-        <v>16</v>
-      </c>
+      <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>3308</v>
       </c>
-      <c r="E9" t="n">
-        <v>329</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>219</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>1260</v>
       </c>
-      <c r="E10" t="n">
-        <v>205</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
+        <v>189</v>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>126</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +797,27 @@
       <c r="D11" t="n">
         <v>1704</v>
       </c>
-      <c r="E11" t="n">
-        <v>316</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>158</v>
+        <v>126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>436</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +835,12 @@
       <c r="D12" t="n">
         <v>1476</v>
       </c>
-      <c r="E12" t="n">
-        <v>104</v>
-      </c>
-      <c r="F12" t="n">
-        <v>16</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +857,20 @@
       <c r="D13" t="n">
         <v>3584</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>490</v>
       </c>
-      <c r="F13" t="n">
-        <v>16</v>
-      </c>
+      <c r="G13" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +887,27 @@
       <c r="D14" t="n">
         <v>2468</v>
       </c>
-      <c r="E14" t="n">
-        <v>383</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>221</v>
+        <v>189</v>
+      </c>
+      <c r="G14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>367</v>
+      </c>
+      <c r="J14" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
